--- a/松本凜多朗ポートフォリオWBS.xlsx
+++ b/松本凜多朗ポートフォリオWBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2230219\Desktop\portforio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A54C454-F03A-4FD8-B21D-5A2131E77C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB188302-D342-4F46-BAB2-9A98C7529F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS一覧" sheetId="1" r:id="rId1"/>
@@ -3883,8 +3883,8 @@
       <c r="H8" s="5">
         <v>0.5</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>17</v>
+      <c r="I8" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>18</v>
@@ -3916,8 +3916,8 @@
       <c r="H9" s="5">
         <v>0.5</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>17</v>
+      <c r="I9" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>18</v>
@@ -3949,8 +3949,8 @@
       <c r="H10" s="5">
         <v>0.5</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>17</v>
+      <c r="I10" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>25</v>
@@ -3982,8 +3982,8 @@
       <c r="H11" s="5">
         <v>1</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>17</v>
+      <c r="I11" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>18</v>

--- a/松本凜多朗ポートフォリオWBS.xlsx
+++ b/松本凜多朗ポートフォリオWBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2230219\Desktop\portforio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB188302-D342-4F46-BAB2-9A98C7529F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333DF8AB-1955-47CA-B585-41B1A540E66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS一覧" sheetId="1" r:id="rId1"/>
@@ -4015,8 +4015,8 @@
       <c r="H12" s="5">
         <v>0.5</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>17</v>
+      <c r="I12" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>18</v>
@@ -4048,8 +4048,8 @@
       <c r="H13" s="5">
         <v>0.5</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>17</v>
+      <c r="I13" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>18</v>
@@ -4081,8 +4081,8 @@
       <c r="H14" s="5">
         <v>0.5</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>17</v>
+      <c r="I14" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J14" s="7" t="s">
         <v>18</v>
@@ -4114,8 +4114,8 @@
       <c r="H15" s="5">
         <v>1</v>
       </c>
-      <c r="I15" s="6" t="s">
-        <v>17</v>
+      <c r="I15" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>18</v>
@@ -4147,8 +4147,8 @@
       <c r="H16" s="5">
         <v>1</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>17</v>
+      <c r="I16" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>18</v>

--- a/松本凜多朗ポートフォリオWBS.xlsx
+++ b/松本凜多朗ポートフォリオWBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2230219\Desktop\portforio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333DF8AB-1955-47CA-B585-41B1A540E66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D988D8D-EAF0-46BD-B7E2-EE22218CC61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/松本凜多朗ポートフォリオWBS.xlsx
+++ b/松本凜多朗ポートフォリオWBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2230219\Desktop\portforio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D988D8D-EAF0-46BD-B7E2-EE22218CC61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EEA640-CF0E-43C4-B31F-7B14758A6CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="218">
   <si>
     <t>No</t>
   </si>
@@ -688,6 +688,13 @@
     <t>完了</t>
     <rPh sb="0" eb="2">
       <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>未着手</t>
+    <rPh sb="0" eb="3">
+      <t>ミチャクシュ</t>
     </rPh>
     <phoneticPr fontId="11"/>
   </si>
@@ -4180,8 +4187,8 @@
       <c r="H17" s="5">
         <v>1</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>17</v>
+      <c r="I17" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>18</v>
@@ -4213,8 +4220,8 @@
       <c r="H18" s="5">
         <v>0.5</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>17</v>
+      <c r="I18" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>25</v>
@@ -4246,8 +4253,8 @@
       <c r="H19" s="5">
         <v>0.5</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>17</v>
+      <c r="I19" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>18</v>
@@ -4279,8 +4286,8 @@
       <c r="H20" s="5">
         <v>0.5</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>17</v>
+      <c r="I20" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>79</v>
@@ -4312,8 +4319,8 @@
       <c r="H21" s="5">
         <v>1</v>
       </c>
-      <c r="I21" s="6" t="s">
-        <v>17</v>
+      <c r="I21" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>18</v>
@@ -4345,8 +4352,8 @@
       <c r="H22" s="5">
         <v>1</v>
       </c>
-      <c r="I22" s="6" t="s">
-        <v>17</v>
+      <c r="I22" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>18</v>
@@ -4378,8 +4385,8 @@
       <c r="H23" s="5">
         <v>1.5</v>
       </c>
-      <c r="I23" s="6" t="s">
-        <v>17</v>
+      <c r="I23" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>18</v>
@@ -4411,8 +4418,8 @@
       <c r="H24" s="5">
         <v>1</v>
       </c>
-      <c r="I24" s="6" t="s">
-        <v>17</v>
+      <c r="I24" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J24" s="7" t="s">
         <v>18</v>
@@ -4444,8 +4451,8 @@
       <c r="H25" s="5">
         <v>1.5</v>
       </c>
-      <c r="I25" s="6" t="s">
-        <v>17</v>
+      <c r="I25" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J25" s="7" t="s">
         <v>18</v>
@@ -4477,8 +4484,8 @@
       <c r="H26" s="5">
         <v>2</v>
       </c>
-      <c r="I26" s="6" t="s">
-        <v>17</v>
+      <c r="I26" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J26" s="7" t="s">
         <v>18</v>
@@ -4510,8 +4517,8 @@
       <c r="H27" s="5">
         <v>1</v>
       </c>
-      <c r="I27" s="6" t="s">
-        <v>17</v>
+      <c r="I27" s="37" t="s">
+        <v>217</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>25</v>
@@ -4543,8 +4550,8 @@
       <c r="H28" s="5">
         <v>1</v>
       </c>
-      <c r="I28" s="6" t="s">
-        <v>17</v>
+      <c r="I28" s="37" t="s">
+        <v>217</v>
       </c>
       <c r="J28" s="7" t="s">
         <v>18</v>
@@ -4576,8 +4583,8 @@
       <c r="H29" s="5">
         <v>2</v>
       </c>
-      <c r="I29" s="6" t="s">
-        <v>17</v>
+      <c r="I29" s="37" t="s">
+        <v>217</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>18</v>
@@ -4609,8 +4616,8 @@
       <c r="H30" s="5">
         <v>1</v>
       </c>
-      <c r="I30" s="6" t="s">
-        <v>17</v>
+      <c r="I30" s="37" t="s">
+        <v>217</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>25</v>
@@ -4642,8 +4649,8 @@
       <c r="H31" s="5">
         <v>1</v>
       </c>
-      <c r="I31" s="6" t="s">
-        <v>17</v>
+      <c r="I31" s="37" t="s">
+        <v>217</v>
       </c>
       <c r="J31" s="7" t="s">
         <v>18</v>
@@ -4675,8 +4682,8 @@
       <c r="H32" s="5">
         <v>0.5</v>
       </c>
-      <c r="I32" s="6" t="s">
-        <v>17</v>
+      <c r="I32" s="37" t="s">
+        <v>217</v>
       </c>
       <c r="J32" s="7" t="s">
         <v>18</v>
@@ -4708,8 +4715,8 @@
       <c r="H33" s="5">
         <v>1.5</v>
       </c>
-      <c r="I33" s="6" t="s">
-        <v>17</v>
+      <c r="I33" s="37" t="s">
+        <v>217</v>
       </c>
       <c r="J33" s="7" t="s">
         <v>18</v>
@@ -4741,8 +4748,8 @@
       <c r="H34" s="5">
         <v>1</v>
       </c>
-      <c r="I34" s="6" t="s">
-        <v>17</v>
+      <c r="I34" s="37" t="s">
+        <v>217</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>25</v>
@@ -4774,8 +4781,8 @@
       <c r="H35" s="5">
         <v>1.5</v>
       </c>
-      <c r="I35" s="6" t="s">
-        <v>17</v>
+      <c r="I35" s="37" t="s">
+        <v>217</v>
       </c>
       <c r="J35" s="8" t="s">
         <v>25</v>
@@ -4807,8 +4814,8 @@
       <c r="H36" s="5">
         <v>1.5</v>
       </c>
-      <c r="I36" s="6" t="s">
-        <v>17</v>
+      <c r="I36" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J36" s="8" t="s">
         <v>25</v>

--- a/松本凜多朗ポートフォリオWBS.xlsx
+++ b/松本凜多朗ポートフォリオWBS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2230219\Desktop\portforio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EEA640-CF0E-43C4-B31F-7B14758A6CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB1C1A1-A039-48D0-9F07-85055A3DD6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4518,7 +4518,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>25</v>
@@ -4551,7 +4551,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J28" s="7" t="s">
         <v>18</v>
@@ -5045,8 +5045,8 @@
       <c r="H43" s="5">
         <v>0.5</v>
       </c>
-      <c r="I43" s="6" t="s">
-        <v>17</v>
+      <c r="I43" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>25</v>
@@ -5078,8 +5078,8 @@
       <c r="H44" s="5">
         <v>0.5</v>
       </c>
-      <c r="I44" s="6" t="s">
-        <v>17</v>
+      <c r="I44" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J44" s="7" t="s">
         <v>18</v>

--- a/松本凜多朗ポートフォリオWBS.xlsx
+++ b/松本凜多朗ポートフォリオWBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2230219\Desktop\portforio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB1C1A1-A039-48D0-9F07-85055A3DD6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47759ADD-C469-40E7-810D-6A52968BCB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="217">
   <si>
     <t>No</t>
   </si>
@@ -688,13 +688,6 @@
     <t>完了</t>
     <rPh sb="0" eb="2">
       <t>カンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="11"/>
-  </si>
-  <si>
-    <t>未着手</t>
-    <rPh sb="0" eb="3">
-      <t>ミチャクシュ</t>
     </rPh>
     <phoneticPr fontId="11"/>
   </si>
@@ -4584,7 +4577,7 @@
         <v>2</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>18</v>
@@ -4617,7 +4610,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>25</v>
@@ -4650,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J31" s="7" t="s">
         <v>18</v>
@@ -4683,7 +4676,7 @@
         <v>0.5</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J32" s="7" t="s">
         <v>18</v>
@@ -4716,7 +4709,7 @@
         <v>1.5</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J33" s="7" t="s">
         <v>18</v>
@@ -4749,7 +4742,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>25</v>
@@ -4782,7 +4775,7 @@
         <v>1.5</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J35" s="8" t="s">
         <v>25</v>
@@ -4913,8 +4906,8 @@
       <c r="H39" s="5">
         <v>1</v>
       </c>
-      <c r="I39" s="6" t="s">
-        <v>17</v>
+      <c r="I39" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J39" s="7" t="s">
         <v>18</v>
@@ -4946,8 +4939,8 @@
       <c r="H40" s="5">
         <v>0.5</v>
       </c>
-      <c r="I40" s="6" t="s">
-        <v>17</v>
+      <c r="I40" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J40" s="7" t="s">
         <v>18</v>
@@ -4979,8 +4972,8 @@
       <c r="H41" s="5">
         <v>1.5</v>
       </c>
-      <c r="I41" s="6" t="s">
-        <v>17</v>
+      <c r="I41" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J41" s="7" t="s">
         <v>18</v>
@@ -5012,8 +5005,8 @@
       <c r="H42" s="5">
         <v>1</v>
       </c>
-      <c r="I42" s="6" t="s">
-        <v>17</v>
+      <c r="I42" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J42" s="7" t="s">
         <v>18</v>

--- a/松本凜多朗ポートフォリオWBS.xlsx
+++ b/松本凜多朗ポートフォリオWBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2230219\Desktop\portforio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47759ADD-C469-40E7-810D-6A52968BCB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB11156A-2C6E-46E6-BF21-5733135F0E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4840,8 +4840,8 @@
       <c r="H37" s="5">
         <v>0.5</v>
       </c>
-      <c r="I37" s="6" t="s">
-        <v>17</v>
+      <c r="I37" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>79</v>
@@ -4873,8 +4873,8 @@
       <c r="H38" s="5">
         <v>1</v>
       </c>
-      <c r="I38" s="6" t="s">
-        <v>17</v>
+      <c r="I38" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>25</v>
@@ -5104,8 +5104,8 @@
       <c r="H45" s="5">
         <v>1</v>
       </c>
-      <c r="I45" s="6" t="s">
-        <v>17</v>
+      <c r="I45" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J45" s="7" t="s">
         <v>18</v>
@@ -5137,8 +5137,8 @@
       <c r="H46" s="5">
         <v>1</v>
       </c>
-      <c r="I46" s="6" t="s">
-        <v>17</v>
+      <c r="I46" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J46" s="7" t="s">
         <v>18</v>
@@ -5170,8 +5170,8 @@
       <c r="H47" s="5">
         <v>0.5</v>
       </c>
-      <c r="I47" s="6" t="s">
-        <v>17</v>
+      <c r="I47" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J47" s="8" t="s">
         <v>25</v>
@@ -5203,8 +5203,8 @@
       <c r="H48" s="5">
         <v>0.5</v>
       </c>
-      <c r="I48" s="6" t="s">
-        <v>17</v>
+      <c r="I48" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J48" s="7" t="s">
         <v>18</v>
@@ -5236,8 +5236,8 @@
       <c r="H49" s="5">
         <v>0.5</v>
       </c>
-      <c r="I49" s="6" t="s">
-        <v>17</v>
+      <c r="I49" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J49" s="8" t="s">
         <v>25</v>
@@ -5269,8 +5269,8 @@
       <c r="H50" s="5">
         <v>0.5</v>
       </c>
-      <c r="I50" s="6" t="s">
-        <v>17</v>
+      <c r="I50" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J50" s="7" t="s">
         <v>18</v>
